--- a/docs/validation/V07_Measure_Unit_Consistency.xlsx
+++ b/docs/validation/V07_Measure_Unit_Consistency.xlsx
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1321,89 +1321,89 @@
       </c>
       <c r="F56" s="19" t="inlineStr"/>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="10" t="inlineStr">
+    <row r="57" ht="29.5" customHeight="1">
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Real vs Nominal Retail Sales</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Sector Sales and Real Sector Sales (both dollars)</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Both in dollars — one axis is correct</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Local Volume vs National Real</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Total Cases YoY % and National Liquor Stores Real YoY %</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Both percentages — one axis is correct</t>
         </is>
       </c>
-      <c r="F57" s="18" t="inlineStr"/>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>National validation</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Sector Sales YoY % for 722 and 4453</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Both percentages — one axis is correct</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="inlineStr"/>
-    </row>
-    <row r="59" ht="42" customHeight="1">
+      <c r="F58" s="18" t="inlineStr"/>
+    </row>
+    <row r="59" ht="29.5" customHeight="1">
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Stress vs Volume</t>
+          <t>Channel split</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Columns: Total Cases YoY % (percent) · Line: Consumer Stress Index (index)</t>
+          <t>Off-Premise Cases and On-Premise Cases (both cases)</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Line on the secondary axis</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="inlineStr"/>
+          <t>Both in cases — one axis is correct</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Income Channel</t>
+          <t>National validation</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>Total Cases YoY % and Real Disposable Income YoY %</t>
+          <t>Sector Sales YoY % for 722 and 4453</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -1413,25 +1413,25 @@
       </c>
       <c r="F60" s="19" t="inlineStr"/>
     </row>
-    <row r="61" ht="28" customHeight="1">
+    <row r="61" ht="42" customHeight="1">
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Stress Components</t>
+          <t>Stress vs Volume</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Three series via Macro Indexed to 100</t>
+          <t>Columns: Total Cases YoY % (percent) · Line: Consumer Stress Index (index)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>All indexed — one axis is correct</t>
+          <t>Line on the secondary axis</t>
         </is>
       </c>
       <c r="F61" s="18" t="inlineStr"/>
@@ -1439,22 +1439,22 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Mix Shift vs Stress</t>
+          <t>Income Channel</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Columns: Mix Shift Magnitude (pp) · Line: Consumer Stress Index</t>
+          <t>Total Cases YoY % and Real Disposable Income YoY %</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Line on the secondary axis</t>
+          <t>Both percentages — one axis is correct</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr"/>
@@ -1462,22 +1462,22 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Share Transfer</t>
+          <t>Stress Components</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Department Store Share % and Warehouse Club Share %</t>
+          <t>Three series via Macro Indexed to 100</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Both percentages — one axis is correct</t>
+          <t>All indexed — one axis is correct</t>
         </is>
       </c>
       <c r="F63" s="18" t="inlineStr"/>
@@ -1485,45 +1485,45 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Pareto</t>
+          <t>Mix Shift vs Stress</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Columns: Total Cases (cases) · Line: Cumulative Cases % (percent)</t>
+          <t>Columns: Mix Shift Magnitude (pp) · Line: Consumer Stress Index</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Line on the secondary axis, 0 to 100%</t>
+          <t>Line on the secondary axis</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr"/>
     </row>
-    <row r="65" ht="42" customHeight="1">
+    <row r="65" ht="28" customHeight="1">
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Assortment Churn</t>
+          <t>Share Transfer</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Columns: New Items, Discontinued Items · Line: Net Assortment Change</t>
+          <t>Department Store Share % and Warehouse Club Share %</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Line on the secondary axis</t>
+          <t>Both percentages — one axis is correct</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr"/>
@@ -1531,40 +1531,40 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Survival by Cohort</t>
+          <t>Pareto</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Cohort Survival 12M % and 24M %</t>
+          <t>Columns: Total Cases (cases) · Line: Cumulative Cases % (percent)</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Both percentages — one axis is correct</t>
+          <t>Line on the secondary axis, 0 to 100%</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr"/>
     </row>
-    <row r="67" ht="28" customHeight="1">
+    <row r="67" ht="42" customHeight="1">
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Share vs Count</t>
+          <t>Assortment Churn</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Columns: Top 10 Supplier Share % · Line: Active Suppliers (count)</t>
+          <t>Columns: New Items, Discontinued Items · Line: Net Assortment Change</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -1577,168 +1577,190 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
         <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Survival by Cohort</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Cohort Survival 12M % and 24M %</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Both percentages — one axis is correct</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Share vs Count</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Columns: Top 10 Supplier Share % · Line: Active Suppliers (count)</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Line on the secondary axis</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr"/>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="12" t="inlineStr">
+        <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>Adjusted vs Raw</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>Total Cases and Seasonally Adjusted Cases</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>Both cases — one axis is correct</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr"/>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="B69" s="20" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr"/>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>Every visual in document 15 that carries more than one measure on its value axes. Taken from the document 15 specification tables.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="8" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="B72" s="14" t="inlineStr">
+    <row r="74" ht="16" customHeight="1">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="B73" s="6" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n"/>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="B74" s="10" t="inlineStr">
+      <c r="F75" s="8" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Every row in the table is Pass</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>No chart mixes units on one scale</t>
         </is>
       </c>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n"/>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="B75" s="12" t="inlineStr">
+      <c r="F76" s="8" t="n"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>Any row fails</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>That chart is misleading as built</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>Fail — list the visuals</t>
         </is>
       </c>
-      <c r="F75" s="8" t="n"/>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="B76" s="21" t="inlineStr">
-        <is>
-          <t>Remember.  Record the check at each report’s report pass for that report’s visuals. The check is complete when all fourteen rows are Pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="F77" s="8" t="n"/>
+    </row>
+    <row r="78" ht="29.5" customHeight="1">
+      <c r="B78" s="21" t="inlineStr">
+        <is>
+          <t>Remember.  Record the check at each report’s report pass for that report’s visuals. The check is complete when all sixteen rows are Pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="B79" s="13" t="inlineStr">
+    <row r="81" ht="20" customHeight="1">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="16" t="n">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="16" t="n">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>Select the Run Summary tab. Find the row for this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="29" customHeight="1">
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr">
-        <is>
-          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="29" customHeight="1">
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
         </is>
       </c>
     </row>
@@ -1750,71 +1772,71 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
+          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="29" customHeight="1">
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="29" customHeight="1">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
           <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="B85" s="17" t="inlineStr">
+    <row r="87" ht="16" customHeight="1">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C85" s="14" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="B86" s="22" t="inlineStr">
+    <row r="88" ht="15" customHeight="1">
+      <c r="B88" s="22" t="inlineStr">
         <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="16" t="n">
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 7.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="n">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1848,7 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Checked by: your name or initials.</t>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
         </is>
       </c>
     </row>
@@ -1838,264 +1860,264 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
           <t>Date checked: today’s date.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="16" t="n">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B94" s="14" t="inlineStr">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="B95" s="6" t="inlineStr">
+    <row r="97" ht="20" customHeight="1">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="n"/>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="8" t="n"/>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>All 14 multi-measure visuals checked (1.5, 1.6, 3.5, 3.12, 4.5, 4.7, 4.8, 5.7, 6.6, 7.5, 7.7, 8.6, 9.6, 10.5) — secondary axis on for 1.6, 4.5, 5.7, 7.5, 7.7, 9.6</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="8" t="n"/>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>R1 only so far: 1.5, 1.6, 3.5, 3.12 Pass — R2 and R3 not yet built</t>
         </is>
       </c>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="8" t="n"/>
     </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="B98" s="20" t="inlineStr">
+    <row r="98" ht="29.5" customHeight="1">
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>All 16 multi-measure visuals checked (1.5, 1.6, 1.7, 3.5, 3.9, 3.12, 4.5, 4.7, 4.8, 5.7, 6.6, 7.5, 7.7, 8.6, 9.6, 10.5) — secondary axis on for 1.6, 4.5, 5.7, 7.5, 7.7, 9.6</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99" ht="29.5" customHeight="1">
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>R1 only so far: 1.5, 1.6, 1.7, 3.5, 3.9, 3.12 Pass — R2 and R3 not yet built</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="8" t="n"/>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="B100" s="20" t="inlineStr">
         <is>
           <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="B99" s="13" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>6.2 In document 26</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="16" t="n">
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="29" customHeight="1">
-      <c r="A101" s="16" t="n">
+    <row r="103" ht="29" customHeight="1">
+      <c r="A103" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="B102" s="6" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Ref in doc 26</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="n"/>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>G7.02, G7.06, G7.07, G7.10, G7.12</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>The page carrying the visual is finished</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>G8.01, G8.03, G8.05</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>The R1, R2 and R3 report passes</t>
         </is>
       </c>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="8" t="n"/>
     </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="105" ht="43" customHeight="1">
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>G7.02, G7.04, G7.06, G7.07, G7.08, G7.10, G7.11, G7.12, G7.13</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>The page carrying the visual is finished</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="8" t="n"/>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>G8.01, G8.03, G8.05</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>The R1, R2 and R3 report passes</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>7. IF IT FAILS</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="B107" s="13" t="inlineStr">
+    <row r="109" ht="20" customHeight="1">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="B108" s="6" t="inlineStr">
+    <row r="110" ht="20" customHeight="1">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="B109" s="10" t="inlineStr">
+      <c r="F110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>Secondary axis off on a combination chart</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>Setting not switched on</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>Format visual → Secondary y-axis → On</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="12" t="inlineStr">
+      <c r="F111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>Two units on one line chart</t>
         </is>
       </c>
-      <c r="C110" s="12" t="inlineStr">
+      <c r="C112" s="12" t="inlineStr">
         <is>
           <t>A measure was added to the wrong well</t>
         </is>
       </c>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="12" t="inlineStr">
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>Move it, or index it through Macro Indexed to 100, per the document 15 spec</t>
         </is>
       </c>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="B111" s="13" t="inlineStr">
+      <c r="F112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="29" customHeight="1">
-      <c r="A112" s="16" t="n">
+    <row r="114" ht="29" customHeight="1">
+      <c r="A114" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 7. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="16" t="n">
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="14" t="inlineStr">
+      <c r="B115" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C114" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="B115" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2129,7 @@
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>What was observed: the same numbers.</t>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -2119,101 +2141,101 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
+          <t>Run ID and Check #: this run and check number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B118" s="14" t="inlineStr">
-        <is>
-          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="29" customHeight="1">
-      <c r="A119" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B119" s="14" t="inlineStr">
-        <is>
-          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="29" customHeight="1">
+      <c r="A121" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B120" s="14" t="inlineStr">
+      <c r="B122" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="8" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="15" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B123" s="14" t="inlineStr">
+      <c r="B125" s="14" t="inlineStr">
         <is>
           <t>After any report visual is added or changed.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="15" t="inlineStr">
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B124" s="14" t="inlineStr">
+      <c r="B126" s="14" t="inlineStr">
         <is>
           <t>At every report pass.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B128" s="14" t="inlineStr">
-        <is>
-          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2247,7 @@
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>Document 25 — when each check is run, and when to re-run it.</t>
+          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -2237,27 +2259,51 @@
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
+          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>Document 25 — when each check is run, and when to re-run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="8" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="29" customHeight="1">
-      <c r="B133" s="14" t="inlineStr">
+    <row r="135" ht="29" customHeight="1">
+      <c r="B135" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="43.5" customHeight="1">
-      <c r="B134" s="14" t="inlineStr">
+    <row r="136" ht="43.5" customHeight="1">
+      <c r="B136" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
@@ -2267,120 +2313,120 @@
   <mergeCells count="114">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="C87:F87"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A134:F134"/>
     <mergeCell ref="C116:F116"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C76:D76"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C93:F93"/>
     <mergeCell ref="C50:F50"/>
-    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="C105:F105"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B133:F133"/>
     <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B80:F80"/>
     <mergeCell ref="E75:F75"/>
-    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="C111:D111"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="B135:F135"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B96:F96"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C96:F96"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="B111:F111"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="C92:F92"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A126:F126"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="A122:F122"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="C98:F98"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="E110:F110"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C91:F91"/>
-    <mergeCell ref="C82:F82"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="C102:F102"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C112:D112"/>
     <mergeCell ref="B48:F48"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="B136:F136"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="C45:F45"/>
+    <mergeCell ref="E77:F77"/>
     <mergeCell ref="C97:F97"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="E108:F108"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="C94:F94"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C84:F84"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C114:F114"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B123:F123"/>
     <mergeCell ref="C95:F95"/>
-    <mergeCell ref="A78:F78"/>
     <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B91:F91"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="C106:F106"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B102:F102"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B132:F132"/>
     <mergeCell ref="C104:F104"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C103:F103"/>
     <mergeCell ref="C85:F85"/>
+    <mergeCell ref="C99:F99"/>
     <mergeCell ref="C117:F117"/>
-    <mergeCell ref="B127:F127"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C118:F118"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="A132:F132"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="C115:F115"/>
-    <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <conditionalFormatting sqref="F55:F68">
+  <conditionalFormatting sqref="F55:F70">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -2389,7 +2435,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F55:F68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F55:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/validation/V07_Measure_Unit_Consistency.xlsx
+++ b/docs/validation/V07_Measure_Unit_Consistency.xlsx
@@ -2313,14 +2313,14 @@
   <mergeCells count="114">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="E111:F111"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B71:F71"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C87:F87"/>
     <mergeCell ref="B42:F42"/>
@@ -2337,8 +2337,8 @@
     <mergeCell ref="C93:F93"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="C105:F105"/>
-    <mergeCell ref="B20:F20"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="C111:D111"/>
@@ -2356,8 +2356,8 @@
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C98:F98"/>
     <mergeCell ref="B82:F82"/>
-    <mergeCell ref="C98:F98"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="E110:F110"/>
     <mergeCell ref="B74:F74"/>
@@ -2367,8 +2367,8 @@
     <mergeCell ref="B126:F126"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="C119:F119"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="C112:D112"/>
@@ -2386,8 +2386,8 @@
     <mergeCell ref="C84:F84"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="E112:F112"/>
-    <mergeCell ref="C12:F12"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C95:F95"/>
@@ -2408,14 +2408,13 @@
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="C104:F104"/>
-    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C85:F85"/>
+    <mergeCell ref="C117:F117"/>
     <mergeCell ref="C99:F99"/>
-    <mergeCell ref="C117:F117"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C118:F118"/>
@@ -2424,6 +2423,7 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <conditionalFormatting sqref="F55:F70">
@@ -2436,7 +2436,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F55:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A"</formula1>
+      <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
